--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.83627</v>
+        <v>17.13017</v>
       </c>
       <c r="D2" t="n">
-        <v>16.98167</v>
+        <v>16.91255</v>
       </c>
       <c r="E2" t="n">
-        <v>17.00335</v>
+        <v>16.94032</v>
       </c>
       <c r="F2" t="n">
-        <v>42.84506</v>
+        <v>42.92318</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05198</v>
+        <v>0.05146</v>
       </c>
       <c r="H2" t="n">
-        <v>1.87193</v>
+        <v>1.81846</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.59889</v>
+        <v>17.18256</v>
       </c>
       <c r="D3" t="n">
-        <v>17.03108</v>
+        <v>16.80013</v>
       </c>
       <c r="E3" t="n">
-        <v>16.95446</v>
+        <v>16.84724</v>
       </c>
       <c r="F3" t="n">
-        <v>42.81667</v>
+        <v>43.49773</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0515</v>
+        <v>0.05087</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83682</v>
+        <v>1.83549</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.25356</v>
+        <v>17.17978</v>
       </c>
       <c r="D4" t="n">
-        <v>16.90081</v>
+        <v>16.68967</v>
       </c>
       <c r="E4" t="n">
-        <v>17.05215</v>
+        <v>16.93512</v>
       </c>
       <c r="F4" t="n">
-        <v>42.65561</v>
+        <v>43.33677</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05085</v>
+        <v>0.05136</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85515</v>
+        <v>1.87155</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.93148</v>
+        <v>16.86105</v>
       </c>
       <c r="D6" t="n">
-        <v>15.9705</v>
+        <v>16.31388</v>
       </c>
       <c r="E6" t="n">
-        <v>16.69</v>
+        <v>16.59902</v>
       </c>
       <c r="F6" t="n">
-        <v>22.33294</v>
+        <v>22.38412</v>
       </c>
       <c r="G6" t="n">
-        <v>35.43568</v>
+        <v>35.11922</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.09782</v>
+        <v>17.06038</v>
       </c>
       <c r="D7" t="n">
-        <v>16.05037</v>
+        <v>16.21666</v>
       </c>
       <c r="E7" t="n">
-        <v>16.94899</v>
+        <v>16.73936</v>
       </c>
       <c r="F7" t="n">
-        <v>21.96582</v>
+        <v>22.25821</v>
       </c>
       <c r="G7" t="n">
-        <v>34.34476</v>
+        <v>34.39305</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.33458</v>
+        <v>17.2123</v>
       </c>
       <c r="D8" t="n">
-        <v>16.12661</v>
+        <v>16.01865</v>
       </c>
       <c r="E8" t="n">
-        <v>16.6955</v>
+        <v>16.75597</v>
       </c>
       <c r="F8" t="n">
-        <v>22.08728</v>
+        <v>22.32438</v>
       </c>
       <c r="G8" t="n">
-        <v>34.54515</v>
+        <v>35.29365</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.59836</v>
+        <v>0.61151</v>
       </c>
       <c r="D10" t="n">
-        <v>1.15498</v>
+        <v>1.14898</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.62477</v>
+        <v>0.61359</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11954</v>
+        <v>1.10269</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.62934</v>
+        <v>0.6079</v>
       </c>
       <c r="D12" t="n">
-        <v>1.14462</v>
+        <v>1.09963</v>
       </c>
     </row>
   </sheetData>
